--- a/proceedings/CameraReadyPapers.xlsx
+++ b/proceedings/CameraReadyPapers.xlsx
@@ -5,13 +5,11 @@
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$J$277</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1q9ktAo1uhMV3LLtMR91t+8BTB3QjOEPoMr9QFmaA5o="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9AtFqsRw/Cb41TaXAO5JyrZ9c7ZBKC8urJJNDFm1s4Q="/>
     </ext>
   </extLst>
 </workbook>
@@ -4671,7 +4669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="12.75" hidden="1" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="3">
         <v>12.0</v>
       </c>
@@ -4694,7 +4692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="12.75" hidden="1" customHeight="1">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="3">
         <v>18.0</v>
       </c>
@@ -4717,7 +4715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="12.75" hidden="1" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="3">
         <v>22.0</v>
       </c>
@@ -4740,7 +4738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="12.75" hidden="1" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="3">
         <v>24.0</v>
       </c>
@@ -4763,7 +4761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="12.75" hidden="1" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="3">
         <v>26.0</v>
       </c>
@@ -4786,7 +4784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="12.75" hidden="1" customHeight="1">
+    <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="3">
         <v>28.0</v>
       </c>
@@ -4809,7 +4807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="12.75" hidden="1" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="3">
         <v>29.0</v>
       </c>
@@ -4832,7 +4830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="12.75" hidden="1" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="3">
         <v>37.0</v>
       </c>
@@ -4855,7 +4853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="12.75" hidden="1" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="3">
         <v>38.0</v>
       </c>
@@ -4878,7 +4876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="12.75" hidden="1" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="3">
         <v>39.0</v>
       </c>
@@ -4901,7 +4899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="12.75" hidden="1" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="3">
         <v>43.0</v>
       </c>
@@ -4924,7 +4922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="12.75" hidden="1" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="3">
         <v>55.0</v>
       </c>
@@ -4947,7 +4945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="12.75" hidden="1" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="3">
         <v>56.0</v>
       </c>
@@ -4970,7 +4968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="12.75" hidden="1" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="3">
         <v>59.0</v>
       </c>
@@ -5057,7 +5055,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" ht="12.75" hidden="1" customHeight="1">
+    <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="3">
         <v>77.0</v>
       </c>
@@ -5141,7 +5139,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" ht="12.75" hidden="1" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="3">
         <v>84.0</v>
       </c>
@@ -5164,7 +5162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="12.75" hidden="1" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="3">
         <v>88.0</v>
       </c>
@@ -5187,7 +5185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="12.75" hidden="1" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="3">
         <v>102.0</v>
       </c>
@@ -5210,7 +5208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" ht="12.75" hidden="1" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="3">
         <v>113.0</v>
       </c>
@@ -5233,7 +5231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="12.75" hidden="1" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="3">
         <v>117.0</v>
       </c>
@@ -5256,7 +5254,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="12.75" hidden="1" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="3">
         <v>121.0</v>
       </c>
@@ -5279,7 +5277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" ht="12.75" hidden="1" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="3">
         <v>122.0</v>
       </c>
@@ -5302,7 +5300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="12.75" hidden="1" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="3">
         <v>124.0</v>
       </c>
@@ -5325,7 +5323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" ht="12.75" hidden="1" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="3">
         <v>126.0</v>
       </c>
@@ -5348,7 +5346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="12.75" hidden="1" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="3">
         <v>128.0</v>
       </c>
@@ -5371,7 +5369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="12.75" hidden="1" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="3">
         <v>131.0</v>
       </c>
@@ -5397,7 +5395,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" ht="12.75" hidden="1" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="3">
         <v>133.0</v>
       </c>
@@ -5423,7 +5421,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33" ht="12.75" hidden="1" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="3">
         <v>136.0</v>
       </c>
@@ -5446,7 +5444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" ht="12.75" hidden="1" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="3">
         <v>138.0</v>
       </c>
@@ -5469,7 +5467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="12.75" hidden="1" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="3">
         <v>147.0</v>
       </c>
@@ -5492,7 +5490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="12.75" hidden="1" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="3">
         <v>150.0</v>
       </c>
@@ -5611,7 +5609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" ht="12.75" hidden="1" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="3">
         <v>168.0</v>
       </c>
@@ -5634,7 +5632,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" ht="12.75" hidden="1" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="3">
         <v>173.0</v>
       </c>
@@ -5657,7 +5655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" ht="12.75" hidden="1" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="3">
         <v>181.0</v>
       </c>
@@ -5680,7 +5678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" ht="12.75" hidden="1" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="3">
         <v>182.0</v>
       </c>
@@ -5738,7 +5736,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" ht="12.75" hidden="1" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="3">
         <v>195.0</v>
       </c>
@@ -5761,7 +5759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" ht="12.75" hidden="1" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="3">
         <v>211.0</v>
       </c>
@@ -5784,7 +5782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" ht="12.75" hidden="1" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="3">
         <v>218.0</v>
       </c>
@@ -5807,7 +5805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" ht="12.75" hidden="1" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="3">
         <v>220.0</v>
       </c>
@@ -5830,7 +5828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" ht="12.75" hidden="1" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="3">
         <v>228.0</v>
       </c>
@@ -5853,7 +5851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" ht="12.75" hidden="1" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="3">
         <v>232.0</v>
       </c>
@@ -5876,7 +5874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" ht="12.75" hidden="1" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="3">
         <v>238.0</v>
       </c>
@@ -5931,7 +5929,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" ht="12.75" hidden="1" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="3">
         <v>257.0</v>
       </c>
@@ -5957,7 +5955,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" ht="12.75" hidden="1" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="3">
         <v>259.0</v>
       </c>
@@ -5980,7 +5978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" ht="12.75" hidden="1" customHeight="1">
+    <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="3">
         <v>261.0</v>
       </c>
@@ -6003,7 +6001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" ht="12.75" hidden="1" customHeight="1">
+    <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="3">
         <v>265.0</v>
       </c>
@@ -6026,7 +6024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" ht="12.75" hidden="1" customHeight="1">
+    <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="3">
         <v>270.0</v>
       </c>
@@ -6052,7 +6050,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" ht="12.75" hidden="1" customHeight="1">
+    <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="3">
         <v>272.0</v>
       </c>
@@ -6075,7 +6073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" ht="12.75" hidden="1" customHeight="1">
+    <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="3">
         <v>276.0</v>
       </c>
@@ -6098,7 +6096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" ht="12.75" hidden="1" customHeight="1">
+    <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="3">
         <v>277.0</v>
       </c>
@@ -6124,7 +6122,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" ht="12.75" hidden="1" customHeight="1">
+    <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="3">
         <v>281.0</v>
       </c>
@@ -6147,7 +6145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" ht="12.75" hidden="1" customHeight="1">
+    <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="3">
         <v>283.0</v>
       </c>
@@ -6170,7 +6168,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" ht="12.75" hidden="1" customHeight="1">
+    <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="3">
         <v>284.0</v>
       </c>
@@ -6193,7 +6191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" ht="12.75" hidden="1" customHeight="1">
+    <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="3">
         <v>288.0</v>
       </c>
@@ -6216,7 +6214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" ht="12.75" hidden="1" customHeight="1">
+    <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="3">
         <v>289.0</v>
       </c>
@@ -6239,7 +6237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" ht="12.75" hidden="1" customHeight="1">
+    <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="3">
         <v>291.0</v>
       </c>
@@ -6262,7 +6260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" ht="12.75" hidden="1" customHeight="1">
+    <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="3">
         <v>292.0</v>
       </c>
@@ -6285,7 +6283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" ht="12.75" hidden="1" customHeight="1">
+    <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="3">
         <v>294.0</v>
       </c>
@@ -6337,7 +6335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" ht="12.75" hidden="1" customHeight="1">
+    <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="3">
         <v>313.0</v>
       </c>
@@ -6360,7 +6358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" ht="12.75" hidden="1" customHeight="1">
+    <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="3">
         <v>320.0</v>
       </c>
@@ -6415,7 +6413,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" ht="12.75" hidden="1" customHeight="1">
+    <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="3">
         <v>330.0</v>
       </c>
@@ -6438,7 +6436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" ht="12.75" hidden="1" customHeight="1">
+    <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="3">
         <v>333.0</v>
       </c>
@@ -6461,7 +6459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" ht="12.75" hidden="1" customHeight="1">
+    <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="3">
         <v>334.0</v>
       </c>
@@ -6484,7 +6482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" ht="12.75" hidden="1" customHeight="1">
+    <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="3">
         <v>338.0</v>
       </c>
@@ -6507,7 +6505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" ht="12.75" hidden="1" customHeight="1">
+    <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="3">
         <v>339.0</v>
       </c>
@@ -6530,7 +6528,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" ht="12.75" hidden="1" customHeight="1">
+    <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="3">
         <v>342.0</v>
       </c>
@@ -6585,7 +6583,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="80" ht="12.75" hidden="1" customHeight="1">
+    <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="3">
         <v>348.0</v>
       </c>
@@ -6640,7 +6638,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" ht="12.75" hidden="1" customHeight="1">
+    <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="3">
         <v>357.0</v>
       </c>
@@ -6663,7 +6661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" ht="12.75" hidden="1" customHeight="1">
+    <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="3">
         <v>358.0</v>
       </c>
@@ -6686,7 +6684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" ht="12.75" hidden="1" customHeight="1">
+    <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="3">
         <v>359.0</v>
       </c>
@@ -6709,7 +6707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" ht="12.75" hidden="1" customHeight="1">
+    <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="3">
         <v>364.0</v>
       </c>
@@ -6732,7 +6730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" ht="12.75" hidden="1" customHeight="1">
+    <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="3">
         <v>366.0</v>
       </c>
@@ -6755,7 +6753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" ht="12.75" hidden="1" customHeight="1">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="3">
         <v>367.0</v>
       </c>
@@ -6778,7 +6776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" ht="12.75" hidden="1" customHeight="1">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="3">
         <v>370.0</v>
       </c>
@@ -6801,7 +6799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" ht="12.75" hidden="1" customHeight="1">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="3">
         <v>373.0</v>
       </c>
@@ -6824,7 +6822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" ht="12.75" hidden="1" customHeight="1">
+    <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="3">
         <v>376.0</v>
       </c>
@@ -6847,7 +6845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" ht="12.75" hidden="1" customHeight="1">
+    <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="3">
         <v>381.0</v>
       </c>
@@ -6870,7 +6868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" ht="12.75" hidden="1" customHeight="1">
+    <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="3">
         <v>391.0</v>
       </c>
@@ -6893,7 +6891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" ht="12.75" hidden="1" customHeight="1">
+    <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="3">
         <v>392.0</v>
       </c>
@@ -6916,7 +6914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" ht="12.75" hidden="1" customHeight="1">
+    <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="3">
         <v>398.0</v>
       </c>
@@ -6971,7 +6969,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="96" ht="12.75" hidden="1" customHeight="1">
+    <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="3">
         <v>402.0</v>
       </c>
@@ -6994,7 +6992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" ht="12.75" hidden="1" customHeight="1">
+    <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="3">
         <v>404.0</v>
       </c>
@@ -7017,7 +7015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" ht="12.75" hidden="1" customHeight="1">
+    <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="3">
         <v>405.0</v>
       </c>
@@ -7040,7 +7038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" ht="12.75" hidden="1" customHeight="1">
+    <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="3">
         <v>408.0</v>
       </c>
@@ -7063,7 +7061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" ht="12.75" hidden="1" customHeight="1">
+    <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="3">
         <v>416.0</v>
       </c>
@@ -7086,7 +7084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" ht="12.75" hidden="1" customHeight="1">
+    <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="3">
         <v>423.0</v>
       </c>
@@ -7109,7 +7107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" ht="12.75" hidden="1" customHeight="1">
+    <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="3">
         <v>427.0</v>
       </c>
@@ -7132,7 +7130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" ht="12.75" hidden="1" customHeight="1">
+    <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="3">
         <v>444.0</v>
       </c>
@@ -7155,7 +7153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" ht="12.75" hidden="1" customHeight="1">
+    <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="3">
         <v>445.0</v>
       </c>
@@ -7178,7 +7176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" ht="12.75" hidden="1" customHeight="1">
+    <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="3">
         <v>453.0</v>
       </c>
@@ -7233,7 +7231,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" ht="12.75" hidden="1" customHeight="1">
+    <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="3">
         <v>458.0</v>
       </c>
@@ -7288,7 +7286,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" ht="12.75" hidden="1" customHeight="1">
+    <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="3">
         <v>478.0</v>
       </c>
@@ -7311,7 +7309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" ht="12.75" hidden="1" customHeight="1">
+    <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="3">
         <v>479.0</v>
       </c>
@@ -7334,7 +7332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" ht="12.75" hidden="1" customHeight="1">
+    <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="3">
         <v>486.0</v>
       </c>
@@ -7357,7 +7355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" ht="12.75" hidden="1" customHeight="1">
+    <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="3">
         <v>493.0</v>
       </c>
@@ -7380,7 +7378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" ht="12.75" hidden="1" customHeight="1">
+    <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="3">
         <v>495.0</v>
       </c>
@@ -7403,7 +7401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" ht="12.75" hidden="1" customHeight="1">
+    <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="3">
         <v>499.0</v>
       </c>
@@ -7426,7 +7424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" ht="12.75" hidden="1" customHeight="1">
+    <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="3">
         <v>500.0</v>
       </c>
@@ -7449,7 +7447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" ht="12.75" hidden="1" customHeight="1">
+    <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="3">
         <v>502.0</v>
       </c>
@@ -7472,7 +7470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" ht="12.75" hidden="1" customHeight="1">
+    <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="3">
         <v>507.0</v>
       </c>
@@ -7495,7 +7493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" ht="12.75" hidden="1" customHeight="1">
+    <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="3">
         <v>509.0</v>
       </c>
@@ -7518,7 +7516,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" ht="12.75" hidden="1" customHeight="1">
+    <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="3">
         <v>511.0</v>
       </c>
@@ -7573,7 +7571,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" ht="12.75" hidden="1" customHeight="1">
+    <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="3">
         <v>517.0</v>
       </c>
@@ -7596,7 +7594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" ht="12.75" hidden="1" customHeight="1">
+    <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="3">
         <v>528.0</v>
       </c>
@@ -7619,7 +7617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" ht="12.75" hidden="1" customHeight="1">
+    <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="3">
         <v>540.0</v>
       </c>
@@ -7642,7 +7640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" ht="12.75" hidden="1" customHeight="1">
+    <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="3">
         <v>543.0</v>
       </c>
@@ -7697,7 +7695,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="126" ht="12.75" hidden="1" customHeight="1">
+    <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="3">
         <v>548.0</v>
       </c>
@@ -7720,7 +7718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" ht="12.75" hidden="1" customHeight="1">
+    <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="3">
         <v>558.0</v>
       </c>
@@ -7746,7 +7744,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="128" ht="12.75" hidden="1" customHeight="1">
+    <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="3">
         <v>566.0</v>
       </c>
@@ -7769,7 +7767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" ht="12.75" hidden="1" customHeight="1">
+    <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="3">
         <v>567.0</v>
       </c>
@@ -7792,7 +7790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" ht="12.75" hidden="1" customHeight="1">
+    <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="3">
         <v>577.0</v>
       </c>
@@ -7815,7 +7813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" ht="12.75" hidden="1" customHeight="1">
+    <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="3">
         <v>588.0</v>
       </c>
@@ -7838,7 +7836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" ht="12.75" hidden="1" customHeight="1">
+    <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="3">
         <v>593.0</v>
       </c>
@@ -7861,7 +7859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" ht="12.75" hidden="1" customHeight="1">
+    <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="3">
         <v>594.0</v>
       </c>
@@ -7884,7 +7882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" ht="12.75" hidden="1" customHeight="1">
+    <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="3">
         <v>596.0</v>
       </c>
@@ -7939,7 +7937,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="136" ht="12.75" hidden="1" customHeight="1">
+    <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="3">
         <v>603.0</v>
       </c>
@@ -7995,7 +7993,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="138" ht="12.75" hidden="1" customHeight="1">
+    <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="3">
         <v>614.0</v>
       </c>
@@ -8018,7 +8016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" ht="12.75" hidden="1" customHeight="1">
+    <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="3">
         <v>626.0</v>
       </c>
@@ -8041,7 +8039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" ht="12.75" hidden="1" customHeight="1">
+    <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="3">
         <v>627.0</v>
       </c>
@@ -8096,7 +8094,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="142" ht="12.75" hidden="1" customHeight="1">
+    <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="3">
         <v>630.0</v>
       </c>
@@ -8120,7 +8118,7 @@
       </c>
       <c r="H142" s="5"/>
     </row>
-    <row r="143" ht="12.75" hidden="1" customHeight="1">
+    <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="3">
         <v>632.0</v>
       </c>
@@ -8175,7 +8173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" ht="12.75" hidden="1" customHeight="1">
+    <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="3">
         <v>646.0</v>
       </c>
@@ -8198,7 +8196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" ht="12.75" hidden="1" customHeight="1">
+    <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="3">
         <v>649.0</v>
       </c>
@@ -8286,7 +8284,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="149" ht="12.75" hidden="1" customHeight="1">
+    <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="3">
         <v>661.0</v>
       </c>
@@ -8341,7 +8339,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="151" ht="12.75" hidden="1" customHeight="1">
+    <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="3">
         <v>666.0</v>
       </c>
@@ -8397,7 +8395,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="153" ht="12.75" hidden="1" customHeight="1">
+    <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="3">
         <v>675.0</v>
       </c>
@@ -8420,7 +8418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" ht="12.75" hidden="1" customHeight="1">
+    <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="3">
         <v>680.0</v>
       </c>
@@ -8443,7 +8441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" ht="12.75" hidden="1" customHeight="1">
+    <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="3">
         <v>690.0</v>
       </c>
@@ -8466,7 +8464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" ht="12.75" hidden="1" customHeight="1">
+    <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="3">
         <v>694.0</v>
       </c>
@@ -8490,7 +8488,7 @@
       </c>
       <c r="H156" s="5"/>
     </row>
-    <row r="157" ht="12.75" hidden="1" customHeight="1">
+    <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="3">
         <v>698.0</v>
       </c>
@@ -8545,7 +8543,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="159" ht="12.75" hidden="1" customHeight="1">
+    <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="3">
         <v>701.0</v>
       </c>
@@ -8600,7 +8598,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="161" ht="12.75" hidden="1" customHeight="1">
+    <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="3">
         <v>705.0</v>
       </c>
@@ -8624,7 +8622,7 @@
       </c>
       <c r="H161" s="5"/>
     </row>
-    <row r="162" ht="12.75" hidden="1" customHeight="1">
+    <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="3">
         <v>707.0</v>
       </c>
@@ -8647,7 +8645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" ht="12.75" hidden="1" customHeight="1">
+    <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="3">
         <v>709.0</v>
       </c>
@@ -8670,7 +8668,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" ht="12.75" hidden="1" customHeight="1">
+    <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="3">
         <v>716.0</v>
       </c>
@@ -8693,7 +8691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" ht="12.75" hidden="1" customHeight="1">
+    <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="3">
         <v>717.0</v>
       </c>
@@ -8780,7 +8778,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="168" ht="12.75" hidden="1" customHeight="1">
+    <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="3">
         <v>722.0</v>
       </c>
@@ -8803,7 +8801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" ht="12.75" hidden="1" customHeight="1">
+    <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="3">
         <v>732.0</v>
       </c>
@@ -8858,7 +8856,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="171" ht="12.75" hidden="1" customHeight="1">
+    <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="3">
         <v>737.0</v>
       </c>
@@ -8882,7 +8880,7 @@
       </c>
       <c r="H171" s="5"/>
     </row>
-    <row r="172" ht="12.75" hidden="1" customHeight="1">
+    <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="3">
         <v>745.0</v>
       </c>
@@ -8905,7 +8903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" ht="12.75" hidden="1" customHeight="1">
+    <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="3">
         <v>751.0</v>
       </c>
@@ -8928,7 +8926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" ht="12.75" hidden="1" customHeight="1">
+    <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="3">
         <v>753.0</v>
       </c>
@@ -8983,7 +8981,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="176" ht="12.75" hidden="1" customHeight="1">
+    <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="3">
         <v>762.0</v>
       </c>
@@ -9038,7 +9036,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="178" ht="12.75" hidden="1" customHeight="1">
+    <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="3">
         <v>768.0</v>
       </c>
@@ -9061,7 +9059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" ht="12.75" hidden="1" customHeight="1">
+    <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="3">
         <v>770.0</v>
       </c>
@@ -9116,7 +9114,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="181" ht="12.75" hidden="1" customHeight="1">
+    <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="3">
         <v>784.0</v>
       </c>
@@ -9171,7 +9169,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="183" ht="12.75" hidden="1" customHeight="1">
+    <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="3">
         <v>787.0</v>
       </c>
@@ -9194,7 +9192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" ht="12.75" hidden="1" customHeight="1">
+    <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="3">
         <v>788.0</v>
       </c>
@@ -9249,7 +9247,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="186" ht="12.75" hidden="1" customHeight="1">
+    <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="3">
         <v>824.0</v>
       </c>
@@ -9336,7 +9334,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="189" ht="12.75" hidden="1" customHeight="1">
+    <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="3">
         <v>828.0</v>
       </c>
@@ -9455,7 +9453,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="193" ht="12.75" hidden="1" customHeight="1">
+    <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="3">
         <v>850.0</v>
       </c>
@@ -9478,7 +9476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" ht="12.75" hidden="1" customHeight="1">
+    <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="3">
         <v>851.0</v>
       </c>
@@ -9533,7 +9531,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="196" ht="12.75" hidden="1" customHeight="1">
+    <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="3">
         <v>857.0</v>
       </c>
@@ -9556,7 +9554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" ht="12.75" hidden="1" customHeight="1">
+    <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="3">
         <v>859.0</v>
       </c>
@@ -9579,7 +9577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" ht="12.75" hidden="1" customHeight="1">
+    <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="3">
         <v>864.0</v>
       </c>
@@ -9634,7 +9632,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="200" ht="12.75" hidden="1" customHeight="1">
+    <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="3">
         <v>866.0</v>
       </c>
@@ -9657,7 +9655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" ht="12.75" hidden="1" customHeight="1">
+    <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="3">
         <v>873.0</v>
       </c>
@@ -9712,7 +9710,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="203" ht="12.75" hidden="1" customHeight="1">
+    <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="3">
         <v>880.0</v>
       </c>
@@ -9799,7 +9797,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="206" ht="12.75" hidden="1" customHeight="1">
+    <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="3">
         <v>898.0</v>
       </c>
@@ -9854,7 +9852,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="208" ht="12.75" hidden="1" customHeight="1">
+    <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="3">
         <v>902.0</v>
       </c>
@@ -9877,7 +9875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" ht="12.75" hidden="1" customHeight="1">
+    <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="3">
         <v>903.0</v>
       </c>
@@ -9900,7 +9898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" ht="12.75" hidden="1" customHeight="1">
+    <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="3">
         <v>914.0</v>
       </c>
@@ -9923,7 +9921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" ht="12.75" hidden="1" customHeight="1">
+    <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="3">
         <v>915.0</v>
       </c>
@@ -10010,7 +10008,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="214" ht="12.75" hidden="1" customHeight="1">
+    <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="3">
         <v>938.0</v>
       </c>
@@ -10161,7 +10159,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="219" ht="12.75" hidden="1" customHeight="1">
+    <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="3">
         <v>955.0</v>
       </c>
@@ -10184,7 +10182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" ht="12.75" hidden="1" customHeight="1">
+    <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="3">
         <v>960.0</v>
       </c>
@@ -10207,7 +10205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" ht="12.75" hidden="1" customHeight="1">
+    <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="3">
         <v>962.0</v>
       </c>
@@ -10294,7 +10292,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="224" ht="12.75" hidden="1" customHeight="1">
+    <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="3">
         <v>986.0</v>
       </c>
@@ -10317,7 +10315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" ht="12.75" hidden="1" customHeight="1">
+    <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="3">
         <v>987.0</v>
       </c>
@@ -10340,7 +10338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" ht="12.75" hidden="1" customHeight="1">
+    <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="3">
         <v>988.0</v>
       </c>
@@ -10395,7 +10393,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="228" ht="12.75" hidden="1" customHeight="1">
+    <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="3">
         <v>992.0</v>
       </c>
@@ -10450,7 +10448,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="230" ht="12.75" hidden="1" customHeight="1">
+    <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="3">
         <v>1004.0</v>
       </c>
@@ -10473,7 +10471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" ht="12.75" hidden="1" customHeight="1">
+    <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="3">
         <v>1006.0</v>
       </c>
@@ -10496,7 +10494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" ht="12.75" hidden="1" customHeight="1">
+    <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="3">
         <v>1007.0</v>
       </c>
@@ -10519,7 +10517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" ht="12.75" hidden="1" customHeight="1">
+    <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="3">
         <v>1013.0</v>
       </c>
@@ -10542,7 +10540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" ht="12.75" hidden="1" customHeight="1">
+    <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="3">
         <v>1015.0</v>
       </c>
@@ -10565,7 +10563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" ht="12.75" hidden="1" customHeight="1">
+    <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="3">
         <v>1024.0</v>
       </c>
@@ -10588,7 +10586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" ht="12.75" hidden="1" customHeight="1">
+    <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="3">
         <v>1029.0</v>
       </c>
@@ -10611,7 +10609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" ht="12.75" hidden="1" customHeight="1">
+    <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="3">
         <v>1030.0</v>
       </c>
@@ -10634,7 +10632,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" ht="12.75" hidden="1" customHeight="1">
+    <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="3">
         <v>1035.0</v>
       </c>
@@ -10657,7 +10655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" ht="12.75" hidden="1" customHeight="1">
+    <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="3">
         <v>1036.0</v>
       </c>
@@ -10680,7 +10678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" ht="12.75" hidden="1" customHeight="1">
+    <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="3">
         <v>1037.0</v>
       </c>
@@ -10703,7 +10701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" ht="12.75" hidden="1" customHeight="1">
+    <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="3">
         <v>1051.0</v>
       </c>
@@ -10790,7 +10788,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="244" ht="12.75" hidden="1" customHeight="1">
+    <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="3">
         <v>1061.0</v>
       </c>
@@ -10813,7 +10811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" ht="12.75" hidden="1" customHeight="1">
+    <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="3">
         <v>1062.0</v>
       </c>
@@ -10868,7 +10866,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="247" ht="12.75" hidden="1" customHeight="1">
+    <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="3">
         <v>1071.0</v>
       </c>
@@ -10891,7 +10889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" ht="12.75" hidden="1" customHeight="1">
+    <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="3">
         <v>1072.0</v>
       </c>
@@ -10914,7 +10912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" ht="12.75" hidden="1" customHeight="1">
+    <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="3">
         <v>1076.0</v>
       </c>
@@ -10969,7 +10967,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="251" ht="12.75" hidden="1" customHeight="1">
+    <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="3">
         <v>1081.0</v>
       </c>
@@ -10992,7 +10990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" ht="12.75" hidden="1" customHeight="1">
+    <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="3">
         <v>1091.0</v>
       </c>
@@ -11047,7 +11045,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="254" ht="12.75" hidden="1" customHeight="1">
+    <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="3">
         <v>1096.0</v>
       </c>
@@ -11070,7 +11068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" ht="12.75" hidden="1" customHeight="1">
+    <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="3">
         <v>1109.0</v>
       </c>
@@ -11125,7 +11123,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="257" ht="12.75" hidden="1" customHeight="1">
+    <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="3">
         <v>1118.0</v>
       </c>
@@ -11180,7 +11178,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="259" ht="12.75" hidden="1" customHeight="1">
+    <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="3">
         <v>1123.0</v>
       </c>
@@ -11235,7 +11233,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="261" ht="12.75" hidden="1" customHeight="1">
+    <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="3">
         <v>1132.0</v>
       </c>
@@ -11258,7 +11256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" ht="12.75" hidden="1" customHeight="1">
+    <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="3">
         <v>1134.0</v>
       </c>
@@ -11313,7 +11311,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="264" ht="12.75" hidden="1" customHeight="1">
+    <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="3">
         <v>1137.0</v>
       </c>
@@ -11336,7 +11334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" ht="12.75" hidden="1" customHeight="1">
+    <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="3">
         <v>1156.0</v>
       </c>
@@ -11359,7 +11357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" ht="12.75" hidden="1" customHeight="1">
+    <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="3">
         <v>1161.0</v>
       </c>
@@ -11382,7 +11380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" ht="12.75" hidden="1" customHeight="1">
+    <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="3">
         <v>1171.0</v>
       </c>
@@ -11405,7 +11403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" ht="12.75" hidden="1" customHeight="1">
+    <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="3">
         <v>1177.0</v>
       </c>
@@ -11428,7 +11426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" ht="12.75" hidden="1" customHeight="1">
+    <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="3">
         <v>1180.0</v>
       </c>
@@ -11451,7 +11449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" ht="12.75" hidden="1" customHeight="1">
+    <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="3">
         <v>1183.0</v>
       </c>
@@ -11474,7 +11472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" ht="12.75" hidden="1" customHeight="1">
+    <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="3">
         <v>1187.0</v>
       </c>
@@ -11497,7 +11495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" ht="12.75" hidden="1" customHeight="1">
+    <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="3">
         <v>1196.0</v>
       </c>
@@ -11616,7 +11614,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="276" ht="12.75" hidden="1" customHeight="1">
+    <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="3">
         <v>1224.0</v>
       </c>
@@ -11639,7 +11637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" ht="12.75" hidden="1" customHeight="1">
+    <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="3">
         <v>1257.0</v>
       </c>
@@ -12386,16 +12384,6 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$J$277">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="yes"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A1:J277">
-      <sortCondition ref="A1:A277"/>
-    </sortState>
-  </autoFilter>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
